--- a/Ice Depth Project/Cleaned Data Sources/Electric.xlsx
+++ b/Ice Depth Project/Cleaned Data Sources/Electric.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7097692be21e5ebd/Documents/Windigo Ice Analysis using R/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Desktop\Professional\Internship Windigo\GitHub\The-Windigo-Data-Team-Summer-2026\Ice Depth Project\Cleaned Data Sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{90CC6907-87ED-4F6A-A153-2E33708F7F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D899DD4-456D-4144-993C-54A622A1F842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CF19EE-28E6-49B9-A779-5D29CE8F90A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{2C695120-188F-48AA-88E0-ADAA39F614CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2C695120-188F-48AA-88E0-ADAA39F614CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Bill date</t>
   </si>
@@ -93,12 +93,6 @@
   </si>
   <si>
     <t>Customer demand (kW)</t>
-  </si>
-  <si>
-    <t>Heating degree days</t>
-  </si>
-  <si>
-    <t>Cooling degree days</t>
   </si>
   <si>
     <t>On-peak</t>
@@ -118,7 +112,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -166,7 +160,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -503,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2345A3C3-FAC1-44D1-B1DF-D5824D0A5EB0}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -511,12 +505,11 @@
     <col min="3" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,13 +517,13 @@
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -539,16 +532,10 @@
         <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -571,18 +558,12 @@
       <c r="G2" s="4">
         <v>222</v>
       </c>
-      <c r="H2" s="4">
-        <v>61</v>
-      </c>
-      <c r="I2" s="4">
-        <v>137</v>
-      </c>
-      <c r="J2" s="3">
+      <c r="H2" s="3">
         <f>E2/B2</f>
         <v>1742.2666666666667</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -605,18 +586,12 @@
       <c r="G3" s="4">
         <v>222</v>
       </c>
-      <c r="H3" s="4">
-        <v>271</v>
-      </c>
-      <c r="I3" s="4">
-        <v>9</v>
-      </c>
-      <c r="J3" s="3">
-        <f t="shared" ref="J3:J15" si="1">E3/B3</f>
+      <c r="H3" s="3">
+        <f t="shared" ref="H3:H15" si="1">E3/B3</f>
         <v>1926.1071428571429</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -639,18 +614,12 @@
       <c r="G4" s="4">
         <v>186</v>
       </c>
-      <c r="H4" s="4">
-        <v>723</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="H4" s="3">
         <f t="shared" si="1"/>
         <v>1767.121212121212</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -673,18 +642,12 @@
       <c r="G5" s="4">
         <v>186</v>
       </c>
-      <c r="H5" s="4">
-        <v>839</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="H5" s="3">
         <f t="shared" si="1"/>
         <v>2075.5172413793102</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -707,18 +670,12 @@
       <c r="G6" s="4">
         <v>186</v>
       </c>
-      <c r="H6" s="4">
-        <v>1404</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="H6" s="3">
         <f t="shared" si="1"/>
         <v>3361.2962962962961</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -741,18 +698,12 @@
       <c r="G7" s="4">
         <v>168</v>
       </c>
-      <c r="H7" s="4">
-        <v>1324</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="H7" s="3">
         <f t="shared" si="1"/>
         <v>2053.457142857143</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -775,18 +726,12 @@
       <c r="G8" s="4">
         <v>168</v>
       </c>
-      <c r="H8" s="4">
-        <v>1092</v>
-      </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="H8" s="3">
         <f t="shared" si="1"/>
         <v>2062.3235294117649</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -809,18 +754,12 @@
       <c r="G9" s="4">
         <v>168</v>
       </c>
-      <c r="H9" s="4">
-        <v>400</v>
-      </c>
-      <c r="I9" s="4">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="H9" s="3">
         <f t="shared" si="1"/>
         <v>1919.5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -843,18 +782,12 @@
       <c r="G10" s="4">
         <v>168</v>
       </c>
-      <c r="H10" s="4">
-        <v>27</v>
-      </c>
-      <c r="I10" s="4">
-        <v>128</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="H10" s="3">
         <f t="shared" si="1"/>
         <v>2170.1428571428573</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -877,18 +810,12 @@
       <c r="G11" s="4">
         <v>157</v>
       </c>
-      <c r="H11" s="4">
-        <v>80</v>
-      </c>
-      <c r="I11" s="4">
-        <v>103</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="H11" s="3">
         <f t="shared" si="1"/>
         <v>2021.0333333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -911,18 +838,12 @@
       <c r="G12" s="4">
         <v>157</v>
       </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
-        <v>246</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="H12" s="3">
         <f t="shared" si="1"/>
         <v>1941.0333333333333</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -945,18 +866,12 @@
       <c r="G13" s="4">
         <v>157</v>
       </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4">
-        <v>318</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="H13" s="3">
         <f t="shared" si="1"/>
         <v>1964.125</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -979,18 +894,12 @@
       <c r="G14" s="4">
         <v>146</v>
       </c>
-      <c r="H14" s="4">
-        <v>132</v>
-      </c>
-      <c r="I14" s="4">
-        <v>47</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="H14" s="3">
         <f t="shared" si="1"/>
         <v>1653.3548387096773</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1013,13 +922,7 @@
       <c r="G15" s="4">
         <v>146</v>
       </c>
-      <c r="H15" s="4">
-        <v>339</v>
-      </c>
-      <c r="I15" s="4">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="H15" s="3">
         <f t="shared" si="1"/>
         <v>1607.3870967741937</v>
       </c>
